--- a/Results/Phase 2/heat climate change breakdown results.xlsx
+++ b/Results/Phase 2/heat climate change breakdown results.xlsx
@@ -1,35 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhinabera/Desktop/Prospective-LCA/Results/Phase 2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\Phase 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC4F4DA-A8B5-7546-89ED-A7970B132BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0662A00B-DB91-4A8C-AE73-137DFD8A88EE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="9330" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="heat" sheetId="1" r:id="rId1"/>
     <sheet name="heatCCS" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -495,10 +482,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -557,7 +544,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -618,8 +605,12 @@
       <c r="T2">
         <v>5.9046749108578142E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U2">
+        <f>T2/D2*100</f>
+        <v>83.160296400402231</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -680,8 +671,12 @@
       <c r="T3">
         <v>5.904674911480768E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="0">T3/D3*100</f>
+        <v>83.410415404273692</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -742,8 +737,12 @@
       <c r="T4">
         <v>5.9046749118603609E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U4">
+        <f t="shared" si="0"/>
+        <v>83.593019857077081</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -804,8 +803,12 @@
       <c r="T5">
         <v>5.9046749123258392E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U5">
+        <f t="shared" si="0"/>
+        <v>83.839284686069931</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -866,8 +869,12 @@
       <c r="T6">
         <v>5.9046749148166149E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U6">
+        <f t="shared" si="0"/>
+        <v>85.059064024584131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -928,8 +935,12 @@
       <c r="T7">
         <v>5.9046749159939023E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7">
+        <f t="shared" si="0"/>
+        <v>85.588391659223575</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -990,8 +1001,12 @@
       <c r="T8">
         <v>5.9046749167304312E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8">
+        <f t="shared" si="0"/>
+        <v>85.859924725244994</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1052,8 +1067,12 @@
       <c r="T9">
         <v>5.9046749125527251E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9">
+        <f t="shared" si="0"/>
+        <v>83.885665208153142</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1114,8 +1133,12 @@
       <c r="T10">
         <v>5.9046749142632041E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10">
+        <f t="shared" si="0"/>
+        <v>84.688434842286568</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1176,225 +1199,9 @@
       <c r="T11">
         <v>5.9046749153491548E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="E13">
-        <f>E2/D2*100</f>
-        <v>5.399173658615225E-2</v>
-      </c>
-      <c r="F13">
-        <f>SUM(F2:L2)/D2*100</f>
-        <v>15.523080871491393</v>
-      </c>
-      <c r="G13">
-        <f>SUM(M2:S2)/D2*100</f>
-        <v>1.2626309915202285</v>
-      </c>
-      <c r="H13">
-        <f>T2/D2*100</f>
-        <v>83.160296400402231</v>
-      </c>
-      <c r="I13">
-        <f>SUM(E13:H13)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="E14">
-        <f t="shared" ref="E14:E22" si="0">E3/D3*100</f>
-        <v>5.1246478856928249E-2</v>
-      </c>
-      <c r="F14">
-        <f t="shared" ref="F14:F22" si="1">SUM(F3:L3)/D3*100</f>
-        <v>15.363624980149732</v>
-      </c>
-      <c r="G14">
-        <f t="shared" ref="G14:G22" si="2">SUM(M3:S3)/D3*100</f>
-        <v>1.1747131367196506</v>
-      </c>
-      <c r="H14">
-        <f t="shared" ref="H14:H22" si="3">T3/D3*100</f>
-        <v>83.410415404273692</v>
-      </c>
-      <c r="I14">
-        <f t="shared" ref="I14:I22" si="4">SUM(E14:H14)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="E15">
+      <c r="U11">
         <f t="shared" si="0"/>
-        <v>4.8349979470716099E-2</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="1"/>
-        <v>15.262520123510285</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="2"/>
-        <v>1.0961100399419281</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="3"/>
-        <v>83.593019857077081</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="4"/>
-        <v>100.00000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="E16">
-        <f t="shared" si="0"/>
-        <v>4.5964401005124653E-2</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="1"/>
-        <v>15.194411851112882</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="2"/>
-        <v>0.92033906181206659</v>
-      </c>
-      <c r="H16">
-        <f t="shared" si="3"/>
-        <v>83.839284686069931</v>
-      </c>
-      <c r="I16">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="5:9" x14ac:dyDescent="0.2">
-      <c r="E17">
-        <f t="shared" si="0"/>
-        <v>3.4339372903139737E-2</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="1"/>
-        <v>14.617308224662468</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="2"/>
-        <v>0.2892883778502528</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="3"/>
-        <v>85.059064024584131</v>
-      </c>
-      <c r="I17">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="5:9" x14ac:dyDescent="0.2">
-      <c r="E18">
-        <f t="shared" si="0"/>
-        <v>2.8526820787683069E-2</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="1"/>
-        <v>14.265186829686947</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="2"/>
-        <v>0.11789469030180329</v>
-      </c>
-      <c r="H18">
-        <f t="shared" si="3"/>
-        <v>85.588391659223575</v>
-      </c>
-      <c r="I18">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="5:9" x14ac:dyDescent="0.2">
-      <c r="E19">
-        <f t="shared" si="0"/>
-        <v>2.5339933861735591E-2</v>
-      </c>
-      <c r="F19">
-        <f t="shared" si="1"/>
-        <v>14.07607944240603</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="2"/>
-        <v>3.865589848723984E-2</v>
-      </c>
-      <c r="H19">
-        <f t="shared" si="3"/>
-        <v>85.859924725244994</v>
-      </c>
-      <c r="I19">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="5:9" x14ac:dyDescent="0.2">
-      <c r="E20">
-        <f t="shared" si="0"/>
-        <v>4.5487952459495253E-2</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="1"/>
-        <v>15.102723397341006</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="2"/>
-        <v>0.96612344204635925</v>
-      </c>
-      <c r="H20">
-        <f t="shared" si="3"/>
-        <v>83.885665208153142</v>
-      </c>
-      <c r="I20">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="5:9" x14ac:dyDescent="0.2">
-      <c r="E21">
-        <f t="shared" si="0"/>
-        <v>3.7975540713207814E-2</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="1"/>
-        <v>14.639072060712676</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="2"/>
-        <v>0.63451755628754192</v>
-      </c>
-      <c r="H21">
-        <f t="shared" si="3"/>
-        <v>84.688434842286568</v>
-      </c>
-      <c r="I21">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="5:9" x14ac:dyDescent="0.2">
-      <c r="E22">
-        <f t="shared" si="0"/>
-        <v>3.0315454260156884E-2</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="1"/>
-        <v>14.461567113370528</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="2"/>
-        <v>0.10916856696244812</v>
-      </c>
-      <c r="H22">
-        <f t="shared" si="3"/>
         <v>85.398948865406865</v>
-      </c>
-      <c r="I22">
-        <f t="shared" si="4"/>
-        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1404,17 +1211,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="5" max="5" width="34.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="62.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" bestFit="1" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1440,7 +1240,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -1451,13 +1251,13 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>2.6580906113421249E-2</v>
+        <v>2.0905914741970111E-2</v>
       </c>
       <c r="E2">
         <v>1.3664136181056731E-2</v>
       </c>
       <c r="F2">
-        <v>6.5310575747539708E-3</v>
+        <v>8.56066468101858E-4</v>
       </c>
       <c r="G2">
         <v>3.8336039758423272E-5</v>
@@ -1466,10 +1266,14 @@
         <v>3.5329556491377819E-4</v>
       </c>
       <c r="I2">
-        <v>5.9940807529383416E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.9940804881393212E-3</v>
+      </c>
+      <c r="J2">
+        <f>I2/D2*100</f>
+        <v>28.671696800263796</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1480,13 +1284,13 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>2.612347210822016E-2</v>
+        <v>2.0680455855597791E-2</v>
       </c>
       <c r="E3">
         <v>1.3489096780868541E-2</v>
       </c>
       <c r="F3">
-        <v>6.2640892645283493E-3</v>
+        <v>8.2107326588092065E-4</v>
       </c>
       <c r="G3">
         <v>3.6277698357408413E-5</v>
@@ -1495,10 +1299,14 @@
         <v>3.3992762600832147E-4</v>
       </c>
       <c r="I3">
-        <v>5.9940807384575344E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.994080484482597E-3</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J11" si="0">I3/D3*100</f>
+        <v>28.98427639282486</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -1509,13 +1317,13 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>2.560212508927924E-2</v>
+        <v>2.048639692225418E-2</v>
       </c>
       <c r="E4">
         <v>1.33644624285746E-2</v>
       </c>
       <c r="F4">
-        <v>5.8874301313849766E-3</v>
+        <v>7.7170220306334953E-4</v>
       </c>
       <c r="G4">
         <v>3.4152481002543928E-5</v>
@@ -1524,10 +1332,14 @@
         <v>3.2199932649807207E-4</v>
       </c>
       <c r="I4">
-        <v>5.9940807218190444E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.9940804831156071E-3</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>29.258832120958733</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1538,13 +1350,13 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>2.4855063409621309E-2</v>
+        <v>2.030138541025028E-2</v>
       </c>
       <c r="E5">
         <v>1.3294858489167911E-2</v>
       </c>
       <c r="F5">
-        <v>5.2405953144520562E-3</v>
+        <v>6.86917527558792E-4</v>
       </c>
       <c r="G5">
         <v>3.2372036379223203E-5</v>
@@ -1553,10 +1365,14 @@
         <v>2.9315687194217079E-4</v>
       </c>
       <c r="I5">
-        <v>5.9940806976799439E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.9940804852021776E-3</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>29.525475055390721</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1567,13 +1383,13 @@
         <v>27</v>
       </c>
       <c r="D6">
-        <v>2.0427745032811102E-2</v>
+        <v>1.9009245089369149E-2</v>
       </c>
       <c r="E6">
         <v>1.268253154292219E-2</v>
       </c>
       <c r="F6">
-        <v>1.632479098912848E-3</v>
+        <v>2.1397922165906921E-4</v>
       </c>
       <c r="G6">
         <v>2.3837886068238092E-5</v>
@@ -1582,10 +1398,14 @@
         <v>9.4815948034028742E-5</v>
       </c>
       <c r="I6">
-        <v>5.9940805568737916E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.9940804906856143E-3</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>31.532448882137786</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1596,13 +1416,13 @@
         <v>28</v>
       </c>
       <c r="D7">
-        <v>1.8823694299895069E-2</v>
+        <v>1.8401536482509442E-2</v>
       </c>
       <c r="E7">
         <v>1.2295029079069019E-2</v>
       </c>
       <c r="F7">
-        <v>4.8583985957198581E-4</v>
+        <v>6.368206188452713E-5</v>
       </c>
       <c r="G7">
         <v>1.9680425680715921E-5</v>
@@ -1611,10 +1431,14 @@
         <v>2.9064429391987172E-5</v>
       </c>
       <c r="I7">
-        <v>5.9940805061813578E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.9940804864831894E-3</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>32.573804324331988</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1625,13 +1449,13 @@
         <v>29</v>
       </c>
       <c r="D8">
-        <v>1.8356469146431711E-2</v>
+        <v>1.8164258924322191E-2</v>
       </c>
       <c r="E8">
         <v>1.2113045190064819E-2</v>
       </c>
       <c r="F8">
-        <v>2.2120492259577711E-4</v>
+        <v>2.8994709454914521E-5</v>
       </c>
       <c r="G8">
         <v>1.7426531398048251E-5</v>
@@ -1640,10 +1464,14 @@
         <v>1.071201068372969E-5</v>
       </c>
       <c r="I8">
-        <v>5.9940804916893296E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.9940804827206774E-3</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>32.999312042918092</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1654,13 +1482,13 @@
         <v>30</v>
       </c>
       <c r="D9">
-        <v>2.4387913831059382E-2</v>
+        <v>2.0151508820576852E-2</v>
       </c>
       <c r="E9">
         <v>1.321033157856997E-2</v>
       </c>
       <c r="F9">
-        <v>4.8754620443347907E-3</v>
+        <v>6.3905723152587253E-4</v>
       </c>
       <c r="G9">
         <v>3.2018767812097631E-5</v>
@@ -1669,10 +1497,14 @@
         <v>2.7602075770184569E-4</v>
       </c>
       <c r="I9">
-        <v>5.9940806826406824E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.9940804849670654E-3</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>29.745070398135482</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1683,13 +1515,13 @@
         <v>31</v>
       </c>
       <c r="D10">
-        <v>2.0846517472921381E-2</v>
+        <v>1.9131023877090401E-2</v>
       </c>
       <c r="E10">
         <v>1.273254351488195E-2</v>
       </c>
       <c r="F10">
-        <v>1.9742739169361762E-3</v>
+        <v>2.5878040115131628E-4</v>
       </c>
       <c r="G10">
         <v>2.6477430636163421E-5</v>
@@ -1698,10 +1530,14 @@
         <v>1.1914204068294749E-4</v>
       </c>
       <c r="I10">
-        <v>5.9940805697841441E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+        <v>5.9940804897380164E-3</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>31.331728653143287</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1712,13 +1548,13 @@
         <v>32</v>
       </c>
       <c r="D11">
-        <v>1.8913824989320718E-2</v>
+        <v>1.8596588672438141E-2</v>
       </c>
       <c r="E11">
         <v>1.251092117905747E-2</v>
       </c>
       <c r="F11">
-        <v>3.6509106617958618E-4</v>
+        <v>4.7854764099468647E-5</v>
       </c>
       <c r="G11">
         <v>2.096078457180763E-5</v>
@@ -1727,7 +1563,11 @@
         <v>2.277145068103715E-5</v>
       </c>
       <c r="I11">
-        <v>5.9940805088308149E-3</v>
+        <v>5.9940804940283544E-3</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>32.232150743389482</v>
       </c>
     </row>
   </sheetData>
